--- a/.cursor/scratch/tax_turbo_parts/ASK.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -645,227 +645,279 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>State Farm bundled home + auto</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED. Previously home=Travelers, car=Geico. Only the HOME share of Prime State Farm is on 524 INSURANCE (50/50 U1/U2, yellow). Auto share and Geico $540.89 credit are personal. Split uses Feb 11 unbundled $157.53 home / $145.25 auto as the ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>STILL OPEN</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>What to confirm</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>REMIND JACOB — ComEd with Megan</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>ComEd is not on these cards. Monarch Adv Plus shows ACH: Jacob Coley $829.15 → Unit 2 ELECTRIC; Megan Gerrard $1,565.26 → Unit 1 ELECTRIC (yellow). User: must have been paid directly or with a check. Double-check with Megan: meters, whether Jake checking ACH is the full picture, and any extra check/direct payments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Soldier Field East Parking $57</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Extra Space $360</t>
+          <t>Soldier Field East Parking $57</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
+          <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>State Farm after August</t>
+          <t>Extra Space $360</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>None on Prime Sep–Dec. Other account?</t>
+          <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Inventory object IDs</t>
+          <t>State Farm declarations / Sep–Dec</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
+          <t>Home vs auto $ is a Feb-charge proxy ($157.53 home / $145.25 auto) until declarations pages. None on Prime Sep–Dec 2025 (524 sold 12/18 — those months may be another account). 2023–24 Excel booked all homeowners on U1; this packet 50/50’s the home share. No 2025 Travelers found on Prime/Sapphire/BoA/Monarch.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>Inventory object IDs</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>827 Grove 1/3 hardware vs locked CapEx</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Grove share $604.12 is pre-close materials on the Grove tab. Do NOT fold into locked TY2025 CapEx $53,660 until CPA says so.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Applied / split totals</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>153</v>
-      </c>
+      <c r="B26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>March HD 100% 524 repairs</t>
+          <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>1358.65</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
+          <t>March HD 100% 524 repairs</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1812.46</v>
+        <v>1358.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
+          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>604.1799999999999</v>
+        <v>1812.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>981.4400000000001</v>
+        <v>604.1799999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>981.4400000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
           <t>Unit 1 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B32" s="9" t="n">
         <v>981.39</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Personal 1/3 (excluded from P&amp;L)</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B33" s="11" t="n">
         <v>604.16</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>827 Grove 1/3 (not in locked $53,660)</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B34" s="13" t="n">
         <v>604.12</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="n">
-        <v>829.15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
+          <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>829.15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
           <t>Unit 1 ELECTRIC ComEd Megan (YELLOW — ask Megan)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
+      <c r="B36" s="15" t="n">
         <v>1565.26</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Inventory parked (Frame Up + LAMA + Hindman)</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n">
-        <v>8043.22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Extra Space HOLD</t>
+          <t>524 INSURANCE home share (Unit 2 50%, yellow proxy)</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>360</v>
+        <v>552.76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
+          <t>524 INSURANCE home share (Unit 1 50%, yellow proxy)</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>552.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>State Farm auto share (personal, excluded)</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>1019.33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Geico auto credit (personal, excluded)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>-540.89</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Inventory parked (Frame Up + LAMA + Hindman)</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>8043.22</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Extra Space HOLD</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
           <t>Soldier Field parking HOLD</t>
         </is>
       </c>
-      <c r="B38" s="17" t="n">
+      <c r="B43" s="17" t="n">
         <v>57</v>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/ASK.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,11 +69,6 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,8 +103,6 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -479,10 +472,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -641,283 +634,305 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED split by transaction 1/3 524 / 1/3 personal / 1/3 Grove. Remaining $1812.46. Extra Space $360 HOLD.</t>
+          <t>CONFIRMED split by transaction 1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (NOT Grove Collaborative). Remaining $1812.46. Extra Space $360 HOLD.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Grove Collaborative orders</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED. “Grove orders” = Grove Collaborative supplies, not 827 N Grove the house. Prime $791.21 → 524 Unit 2 SUPPLIES (8 charges). Betty’s Pizza / KS Grove is unrelated (personal dining).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>State Farm bundled home + auto</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>CONFIRMED. Previously home=Travelers, car=Geico. Only the HOME share of Prime State Farm is on 524 INSURANCE (50/50 U1/U2, yellow). Auto share and Geico $540.89 credit are personal. Split uses Feb 11 unbundled $157.53 home / $145.25 auto as the ratio.</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>STILL OPEN</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>What to confirm</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>REMIND JACOB — ComEd with Megan</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>ComEd is not on these cards. Monarch Adv Plus shows ACH: Jacob Coley $829.15 → Unit 2 ELECTRIC; Megan Gerrard $1,565.26 → Unit 1 ELECTRIC (yellow). User: must have been paid directly or with a check. Double-check with Megan: meters, whether Jake checking ACH is the full picture, and any extra check/direct payments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Soldier Field East Parking $57</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Extra Space $360</t>
+          <t>Soldier Field East Parking $57</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
+          <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>State Farm declarations / Sep–Dec</t>
+          <t>Extra Space $360</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Home vs auto $ is a Feb-charge proxy ($157.53 home / $145.25 auto) until declarations pages. None on Prime Sep–Dec 2025 (524 sold 12/18 — those months may be another account). 2023–24 Excel booked all homeowners on U1; this packet 50/50’s the home share. No 2025 Travelers found on Prime/Sapphire/BoA/Monarch.</t>
+          <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Inventory object IDs</t>
+          <t>State Farm declarations / Sep–Dec</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
+          <t>Home vs auto $ is a Feb-charge proxy ($157.53 home / $145.25 auto) until declarations pages. None on Prime Sep–Dec 2025 (524 sold 12/18 — those months may be another account). 2023–24 Excel booked all homeowners on U1; this packet 50/50’s the home share. No 2025 Travelers found on Prime/Sapphire/BoA/Monarch.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>827 Grove 1/3 hardware vs locked CapEx</t>
+          <t>Inventory object IDs</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Grove share $604.12 is pre-close materials on the Grove tab. Do NOT fold into locked TY2025 CapEx $53,660 until CPA says so.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+          <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>827 N Grove the house — HD 1/3 vs locked CapEx</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>HD/Lowe’s/IKEA 1/3 $604.12 is pre-close materials for 827 N Grove the house (Q5 split), not Grove Collaborative. Do NOT fold into locked TY2025 CapEx $53,660 until CPA says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Applied / split totals</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>153</v>
-      </c>
+      <c r="B27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>March HD 100% 524 repairs</t>
+          <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1358.65</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
+          <t>March HD 100% 524 repairs</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>1812.46</v>
+        <v>1358.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
+          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>604.1799999999999</v>
+        <v>1812.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>981.4400000000001</v>
+        <v>604.1799999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
+          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>981.4400000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
           <t>Unit 1 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B33" s="9" t="n">
         <v>981.39</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Personal 1/3 (excluded from P&amp;L)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B34" s="11" t="n">
         <v>604.16</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>827 Grove 1/3 (not in locked $53,660)</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>827 N Grove the house 1/3 HD/Lowe’s/IKEA (not Grove Collaborative; not locked $53,660)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
         <v>604.12</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>524 Unit 2 SUPPLIES (Grove Collaborative)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>791.21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
+      <c r="B37" s="13" t="n">
         <v>829.15</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Unit 1 ELECTRIC ComEd Megan (YELLOW — ask Megan)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
+      <c r="B38" s="13" t="n">
         <v>1565.26</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>524 INSURANCE home share (Unit 2 50%, yellow proxy)</t>
         </is>
       </c>
-      <c r="B37" s="17" t="n">
+      <c r="B39" s="15" t="n">
         <v>552.76</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>524 INSURANCE home share (Unit 1 50%, yellow proxy)</t>
         </is>
       </c>
-      <c r="B38" s="17" t="n">
+      <c r="B40" s="15" t="n">
         <v>552.7</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>State Farm auto share (personal, excluded)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B41" s="11" t="n">
         <v>1019.33</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Geico auto credit (personal, excluded)</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B42" s="11" t="n">
         <v>-540.89</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Inventory parked (Frame Up + LAMA + Hindman)</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B43" s="9" t="n">
         <v>8043.22</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>Extra Space HOLD</t>
         </is>
       </c>
-      <c r="B42" s="17" t="n">
+      <c r="B44" s="15" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Soldier Field parking HOLD</t>
         </is>
       </c>
-      <c r="B43" s="17" t="n">
+      <c r="B45" s="15" t="n">
         <v>57</v>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/ASK.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -662,278 +662,545 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BoA checking folders = 9922 + 0203</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>JSC Adv Plus 4830 6191 9922 (Jake) and joint Adv Plus 4830 7359 0203 (Megan+Jacob). 12 statements each for 2025. Monarch credits on those two accounts match the statement deposit sections sampled.</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>GCM board fee → Consultant</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Gates Capital BOM PAYMEN $21500.00: 2/12 $4,100 + 4/18 $9,200 + 9/13 $4,100 + 11/13 $4,100. Equals Form 1099-NEC $21,500. Booked EPGC Consultant (cash-basis month) and GCM tab. Income tab GCM actual was already $21,500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>GCM reimbursements EXCLUDED</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>JAKE C / SEFOF on 9922 $3033.83 (board meeting $1,150.99; 5/22 $609.02 unlabeled; 11/05 $1,273.82). Plus Checking 8507 SEFOF $2180.86 (Wharton / annual conference / education committee) — that account is not in the two folders. Total reimbursement $5214.69 kept off Consultant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>LTR rent → 216 Oak Park STR / RENTAL INCOME</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>JOHN T DELACH 8×$1,450 ($11600.00) + Joan Friedberger 2×$1,950 ($3900.00) on joint 0203. Ava L Hernandez 8×$500 ($4000.00) same rent memo / $1,950 combined — included yellow (ASK). TY2025 cash total $19500.00. Oct–Nov 2025: no rent on 0203.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Bear Creek not income</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Four wires $9,500 on Jake 9922 (1/9, 4/10, 7/10, 10/9) = $38000.00. Annual gift — excluded from Consultant / rental / Income tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>UTMA not income</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Emma CMA 2T48 + sibling CMA 4729: Thomas wires $5,000 each Nov/Dec = $10000.00 (not ~$10k each). Treasury-note maturities $10,000 each 12/31 are principal, not gifts. Excluded from income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>STILL OPEN</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>What to confirm</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>REMIND JACOB — ComEd with Megan</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>ComEd is not on these cards. Monarch Adv Plus shows ACH: Jacob Coley $829.15 → Unit 2 ELECTRIC; Megan Gerrard $1,565.26 → Unit 1 ELECTRIC (yellow). User: must have been paid directly or with a check. Double-check with Megan: meters, whether Jake checking ACH is the full picture, and any extra check/direct payments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Joint 0203 statements show ComEd ACH (e.g. 1/21 Jacob $59.04 + Megan $132.94). ComEd is not on these cards. Monarch Adv Plus shows ACH: Jacob Coley $829.15 → Unit 2 ELECTRIC; Megan Gerrard $1,565.26 → Unit 1 ELECTRIC (yellow). User: must have been paid directly or with a check. Double-check with Megan: meters, whether Jake checking ACH is the full picture, and any extra check/direct payments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Soldier Field East Parking $57</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Extra Space $360</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>State Farm declarations / Sep–Dec</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Home vs auto $ is a Feb-charge proxy ($157.53 home / $145.25 auto) until declarations pages. None on Prime Sep–Dec 2025 (524 sold 12/18 — those months may be another account). 2023–24 Excel booked all homeowners on U1; this packet 50/50’s the home share. No 2025 Travelers found on Prime/Sapphire/BoA/Monarch.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Inventory object IDs</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>827 N Grove the house — HD 1/3 vs locked CapEx</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>HD/Lowe’s/IKEA 1/3 $604.12 is pre-close materials for 827 N Grove the house (Q5 split), not Grove Collaborative. Do NOT fold into locked TY2025 CapEx $53,660 until CPA says so.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Ava L Hernandez $500/mo rent</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Eight Zelle credits on joint 0203, same days as Delach, memo “rent”. Delach $1,450 + Ava $500 = $1,950, which is Joan’s later rent. Is Ava Delach’s roommate/co-tenant at 216 Oak Park? I booked her on STR / RENTAL INCOME (yellow) so the $1,950 unit rent is complete. Say if she should be excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Oak Park vacant Oct–Nov 2025?</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>No Delach / Ava / Joan rent on 0203 in October or November. Last Delach/Ava is 8/29 “September Rent”. Joan starts 12/1. Confirm those two months were vacant (and held for rent) for Sch E. Jan 2025 occupancy cash hit 12/31/2024 ($1,450+$500) — left out of TY2025 cash. Correct?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Joan Friedberger Dec cash</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>12/1 $1,950 memo “rent” and 12/31 $1,950 memo “January rent” both in TY2025 cash. Is 12/1 December occupancy and 12/31 January 2026 prepaid? Also: Checking 8507 Zelle OUT $675 to Joan on 12/1 — deposit return / repair? Not on these two BoA folders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>GCM on EPGC Consultant vs personal 1099</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>You said board fee → consultant line, so I put BOM $21,500 on EPGC LLC Consultant. Historically GCM lived on its own tab + Income “GCM Boards”, and EPGC Consultant was empty. 1099-NEC is in Jacob’s name from Gates Capital. Confirm: EPGC LLC (this booking) vs personal Sch C / GCM tab only (then I will zero EPGC Consultant so LLC P&amp;L is not mixed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>May 22 Gates $609.02</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Statement says GATES CAPITAL MA DES:JAKE C $609.02 — no PMT INFO. Same DES as reimbursements, not BOM PAYMEN. I excluded it from Consultant. Confirm it is reimbursement (or board fee if you say so).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Bear Creek $38,000 vs kids’ UTMA ~$10k each</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Bear Creek to Jake 9922 is $9,500×4 = $38,000 (not ~$10k). Thomas wires into the two CMA-Edge UTMAs are $5,000 each in late Nov. Are Bear Creek gifts to you (parents), and Thomas the kids’ UTMA? Is more UTMA cash coming that never hit these checkings (e.g. directly at Merrill)? 2/25 $36,000 9922→National Financial was reversed 2/27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Freeman’s / CIBC $11,000 wire 12/24 on joint 0203</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>ORIG:FREEMAN'S LLC via CIBC Bank USA; PMT DET Sale 6428 Contract 303468. Not W-2 payroll (those are DIR DEP on 9922). Art sale? Consignment? Other? HOLD off income until you say.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Checking 8507 (NOW) 2025 statements?</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Third checking in Monarch — Airbnb/VRBO STR, Megan Zelle, and the three GCM SEFOF reimbursements. Not in the two folders you just added. Upload 2025 statements if you want that account reconciled the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Applied / split totals</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="B41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B42" s="9" t="n">
         <v>153</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>March HD 100% 524 repairs</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>1358.65</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n">
-        <v>1812.46</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n">
-        <v>604.1799999999999</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n">
-        <v>981.4400000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Unit 1 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>981.39</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Personal 1/3 (excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>604.16</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>827 N Grove the house 1/3 HD/Lowe’s/IKEA (not Grove Collaborative; not locked $53,660)</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n">
-        <v>604.12</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>524 Unit 2 SUPPLIES (Grove Collaborative)</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n">
-        <v>791.21</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="n">
-        <v>829.15</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>Unit 1 ELECTRIC ComEd Megan (YELLOW — ask Megan)</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n">
-        <v>1565.26</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>524 INSURANCE home share (Unit 2 50%, yellow proxy)</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n">
-        <v>552.76</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>524 INSURANCE home share (Unit 1 50%, yellow proxy)</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n">
-        <v>552.7</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>State Farm auto share (personal, excluded)</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>1019.33</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Geico auto credit (personal, excluded)</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>-540.89</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
+          <t>March HD 100% 524 repairs</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>1358.65</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>1812.46</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>604.1799999999999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>981.4400000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Unit 1 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>981.39</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Personal 1/3 (excluded from P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>604.16</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>827 N Grove the house 1/3 HD/Lowe’s/IKEA (not Grove Collaborative; not locked $53,660)</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>604.12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>524 Unit 2 SUPPLIES (Grove Collaborative)</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>791.21</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="n">
+        <v>829.15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Unit 1 ELECTRIC ComEd Megan (YELLOW — ask Megan)</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="n">
+        <v>1565.26</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>524 INSURANCE home share (Unit 2 50%, yellow proxy)</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="n">
+        <v>552.76</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>524 INSURANCE home share (Unit 1 50%, yellow proxy)</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="n">
+        <v>552.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>State Farm auto share (personal, excluded)</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>1019.33</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Geico auto credit (personal, excluded)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>-540.89</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
           <t>Inventory parked (Frame Up + LAMA + Hindman)</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
+      <c r="B57" s="9" t="n">
         <v>8043.22</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>Extra Space HOLD</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n">
+      <c r="B58" s="15" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>Soldier Field parking HOLD</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
+      <c r="B59" s="15" t="n">
         <v>57</v>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Checking inflows 2026-09-18</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>216 Oak Park STR / RENTAL INCOME (cash, incl. Ava yellow)</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Delach 8 × $1,450</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ava Hernandez 8 × $500 (ASK roommate)</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Joan Friedberger 2 × $1,950 (ASK Dec vs Jan prepaid)</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>EPGC Consultant = GCM BOM = 1099-NEC</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>GCM reimbursements EXCLUDED (9922 + 8507)</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>5214.69</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Bear Creek gift EXCLUDED (4 × $9,500)</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>UTMA Thomas wires EXCLUDED (2 × $5,000)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Freeman’s CIBC $11,000 12/24 HOLD</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="n">
+        <v>11000</v>
       </c>
     </row>
   </sheetData>

--- a/.cursor/scratch/tax_turbo_parts/ASK.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK.xlsx
@@ -665,498 +665,492 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>BoA checking folders = 9922 + 0203</t>
+          <t>Ava L Hernandez $500/mo rent</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>JSC Adv Plus 4830 6191 9922 (Jake) and joint Adv Plus 4830 7359 0203 (Megan+Jacob). 12 statements each for 2025. Monarch credits on those two accounts match the statement deposit sections sampled.</t>
+          <t>CONFIRMED Delach co-tenant. Keep eight $500 Zelle credits on 216 Oak Park STR / RENTAL INCOME. Delach $1,450 + Ava $500 = $1,950 unit rent (same as Joan later).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>GCM board fee → Consultant</t>
+          <t>Oak Park vacant Oct + half Nov</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Gates Capital BOM PAYMEN $21500.00: 2/12 $4,100 + 4/18 $9,200 + 9/13 $4,100 + 11/13 $4,100. Equals Form 1099-NEC $21,500. Booked EPGC Consultant (cash-basis month) and GCM tab. Income tab GCM actual was already $21,500.</t>
+          <t>CONFIRMED vacant October and the first half of November (held for rent). Occupancy: Delach/Ava through September; Joan from mid-November. Cash-basis months stay as deposited (Sep cash is $0 because September rent hit 8/29). Jan 2025 occupancy cash hit 12/31/2024 — still out of TY2025.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>GCM reimbursements EXCLUDED</t>
+          <t>Joan 12/1 Zelle OUT $675 = repair</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>JAKE C / SEFOF on 9922 $3033.83 (board meeting $1,150.99; 5/22 $609.02 unlabeled; 11/05 $1,273.82). Plus Checking 8507 SEFOF $2180.86 (Wharton / annual conference / education committee) — that account is not in the two folders. Total reimbursement $5214.69 kept off Consultant.</t>
+          <t>CONFIRMED. Checking 8507 Zelle to Joan 12/1 $675 → 216 INTERIOR MAINTENANCE (December). CPA may reclass interior vs exterior. 12/1 $1,950 IN on joint 0203 stays December occupancy cash; 12/31 $1,950 “January rent” stays Jan 2026 prepaid cash in TY2025.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>LTR rent → 216 Oak Park STR / RENTAL INCOME</t>
+          <t>GCM off EPGC Consultant</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>JOHN T DELACH 8×$1,450 ($11600.00) + Joan Friedberger 2×$1,950 ($3900.00) on joint 0203. Ava L Hernandez 8×$500 ($4000.00) same rent memo / $1,950 combined — included yellow (ASK). TY2025 cash total $19500.00. Oct–Nov 2025: no rent on 0203.</t>
+          <t>CONFIRMED. BOM PAYMEN $21,500 stays on the GCM tab + Income E7 (personal 1099-NEC, Jacob’s name). EPGC Consultant zeroed. JAKE C / SEFOF reimbursements $5,214.69 still excluded.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Bear Creek not income</t>
+          <t>May 22 Gates $609.02</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Four wires $9,500 on Jake 9922 (1/9, 4/10, 7/10, 10/9) = $38000.00. Annual gift — excluded from Consultant / rental / Income tab.</t>
+          <t>CONFIRMED reimbursement (JAKE C, not BOM PAYMEN). Excluded from income.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>UTMA not income</t>
+          <t>Bear Creek $38,000 to Jake from parents</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Emma CMA 2T48 + sibling CMA 4729: Thomas wires $5,000 each Nov/Dec = $10000.00 (not ~$10k each). Treasury-note maturities $10,000 each 12/31 are principal, not gifts. Excluded from income.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
+          <t>CONFIRMED annual gift to Jacob from parents — not income. User: UTMA was not ~$10k each; Thomas wires $5,000 each (Emma CMA 2T48 + Phoebe CMA 4729) = $10,000 excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Freeman’s / CIBC $11,000 art-sale settlement</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED Sale 6428 Contract 303468. Check went to Megan (joint 0203 2025-12-24). Booked Art Sales Sale Price $11,000; Cost and object name yellow TBD. Not Mercury, not W-2 payroll.</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Checking 8507 statements</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>WAIT-MEGAN. Jacob asked Megan to send 2025 NOW 8507 statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>STILL OPEN</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>What to confirm</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>REMIND JACOB — ComEd with Megan</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Joint 0203 statements show ComEd ACH (e.g. 1/21 Jacob $59.04 + Megan $132.94). ComEd is not on these cards. Monarch Adv Plus shows ACH: Jacob Coley $829.15 → Unit 2 ELECTRIC; Megan Gerrard $1,565.26 → Unit 1 ELECTRIC (yellow). User: must have been paid directly or with a check. Double-check with Megan: meters, whether Jake checking ACH is the full picture, and any extra check/direct payments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Soldier Field East Parking $57</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Extra Space $360</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>State Farm declarations / Sep–Dec</t>
+          <t>Soldier Field East Parking $57</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Home vs auto $ is a Feb-charge proxy ($157.53 home / $145.25 auto) until declarations pages. None on Prime Sep–Dec 2025 (524 sold 12/18 — those months may be another account). 2023–24 Excel booked all homeowners on U1; this packet 50/50’s the home share. No 2025 Travelers found on Prime/Sapphire/BoA/Monarch.</t>
+          <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Inventory object IDs</t>
+          <t>Extra Space $360</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
+          <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>827 N Grove the house — HD 1/3 vs locked CapEx</t>
+          <t>State Farm declarations / Sep–Dec</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>HD/Lowe’s/IKEA 1/3 $604.12 is pre-close materials for 827 N Grove the house (Q5 split), not Grove Collaborative. Do NOT fold into locked TY2025 CapEx $53,660 until CPA says so.</t>
+          <t>Home vs auto $ is a Feb-charge proxy ($157.53 home / $145.25 auto) until declarations pages. None on Prime Sep–Dec 2025 (524 sold 12/18 — those months may be another account). 2023–24 Excel booked all homeowners on U1; this packet 50/50’s the home share. No 2025 Travelers found on Prime/Sapphire/BoA/Monarch.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Ava L Hernandez $500/mo rent</t>
+          <t>Inventory object IDs</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Eight Zelle credits on joint 0203, same days as Delach, memo “rent”. Delach $1,450 + Ava $500 = $1,950, which is Joan’s later rent. Is Ava Delach’s roommate/co-tenant at 216 Oak Park? I booked her on STR / RENTAL INCOME (yellow) so the $1,950 unit rent is complete. Say if she should be excluded.</t>
+          <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Oak Park vacant Oct–Nov 2025?</t>
+          <t>827 N Grove the house — HD 1/3 vs locked CapEx</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>No Delach / Ava / Joan rent on 0203 in October or November. Last Delach/Ava is 8/29 “September Rent”. Joan starts 12/1. Confirm those two months were vacant (and held for rent) for Sch E. Jan 2025 occupancy cash hit 12/31/2024 ($1,450+$500) — left out of TY2025 cash. Correct?</t>
+          <t>HD/Lowe’s/IKEA 1/3 $604.12 is pre-close materials for 827 N Grove the house (Q5 split), not Grove Collaborative. Do NOT fold into locked TY2025 CapEx $53,660 until CPA says so.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Joan Friedberger Dec cash</t>
+          <t>WAIT MEGAN — Checking 8507 (NOW) 2025 statements</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>12/1 $1,950 memo “rent” and 12/31 $1,950 memo “January rent” both in TY2025 cash. Is 12/1 December occupancy and 12/31 January 2026 prepaid? Also: Checking 8507 Zelle OUT $675 to Joan on 12/1 — deposit return / repair? Not on these two BoA folders.</t>
+          <t>Jacob asked Megan to send them. Needed to (a) book Joan’s half-November rent if the deposit is there, (b) keep reconciling Airbnb/VRBO vs platform, (c) keep the three SEFOF reimbursements tied. 11/30 Zelle FROM MEGAN $1,950 on 8507 is a Megan transfer, not Joan rent.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>GCM on EPGC Consultant vs personal 1099</t>
+          <t>Joan half-November rent $975</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>You said board fee → consultant line, so I put BOM $21,500 on EPGC LLC Consultant. Historically GCM lived on its own tab + Income “GCM Boards”, and EPGC Consultant was empty. 1099-NEC is in Jacob’s name from Gates Capital. Confirm: EPGC LLC (this booking) vs personal Sch C / GCM tab only (then I will zero EPGC Consultant so LLC P&amp;L is not mixed).</t>
+          <t>User: Joan paid half of November. Not on joint 0203. Nov cash on 216 Oak Park stays $0 until 8507 (or another account) shows the deposit. Do not invent $975.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>May 22 Gates $609.02</t>
+          <t>Sale 6428 object / Cost</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Statement says GATES CAPITAL MA DES:JAKE C $609.02 — no PMT INFO. Same DES as reimbursements, not BOM PAYMEN. I excluded it from Consultant. Confirm it is reimbursement (or board fee if you say so).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Bear Creek $38,000 vs kids’ UTMA ~$10k each</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Bear Creek to Jake 9922 is $9,500×4 = $38,000 (not ~$10k). Thomas wires into the two CMA-Edge UTMAs are $5,000 each in late Nov. Are Bear Creek gifts to you (parents), and Thomas the kids’ UTMA? Is more UTMA cash coming that never hit these checkings (e.g. directly at Merrill)? 2/25 $36,000 9922→National Financial was reversed 2/27.</t>
-        </is>
-      </c>
-    </row>
+          <t>Freeman’s $11,000 is Art Sales Sale Price (check to Megan 12/24). Cost and object blank yellow — Income E8 net stays $0 until Cost is filled. 2026-01-08 Hindman SETTLEMENT SALE 6428 $937.83 is 2026, not TY2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Freeman’s / CIBC $11,000 wire 12/24 on joint 0203</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>ORIG:FREEMAN'S LLC via CIBC Bank USA; PMT DET Sale 6428 Contract 303468. Not W-2 payroll (those are DIR DEP on 9922). Art sale? Consignment? Other? HOLD off income until you say.</t>
-        </is>
-      </c>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Applied / split totals</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Checking 8507 (NOW) 2025 statements?</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Third checking in Monarch — Airbnb/VRBO STR, Megan Zelle, and the three GCM SEFOF reimbursements. Not in the two folders you just added. Upload 2025 statements if you want that account reconciled the same way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>March HD 100% 524 repairs</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>1358.65</v>
+      </c>
+    </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Applied / split totals</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n"/>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>1812.46</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
+          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>153</v>
+        <v>604.1799999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>March HD 100% 524 repairs</t>
+          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
         </is>
       </c>
       <c r="B43" s="9" t="n">
-        <v>1358.65</v>
+        <v>981.4400000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
+          <t>Unit 1 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>1812.46</v>
+        <v>981.39</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="n">
-        <v>604.1799999999999</v>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Personal 1/3 (excluded from P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>604.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+          <t>827 N Grove the house 1/3 HD/Lowe’s/IKEA (not Grove Collaborative; not locked $53,660)</t>
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>981.4400000000001</v>
+        <v>604.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Unit 1 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+          <t>524 Unit 2 SUPPLIES (Grove Collaborative)</t>
         </is>
       </c>
       <c r="B47" s="9" t="n">
-        <v>981.39</v>
+        <v>791.21</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Personal 1/3 (excluded from P&amp;L)</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>604.16</v>
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>829.15</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>827 N Grove the house 1/3 HD/Lowe’s/IKEA (not Grove Collaborative; not locked $53,660)</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>604.12</v>
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Unit 1 ELECTRIC ComEd Megan (YELLOW — ask Megan)</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>1565.26</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>524 Unit 2 SUPPLIES (Grove Collaborative)</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="n">
-        <v>791.21</v>
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>524 INSURANCE home share (Unit 2 50%, yellow proxy)</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n">
+        <v>552.76</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="n">
-        <v>829.15</v>
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>524 INSURANCE home share (Unit 1 50%, yellow proxy)</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n">
+        <v>552.7</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>Unit 1 ELECTRIC ComEd Megan (YELLOW — ask Megan)</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="n">
-        <v>1565.26</v>
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>State Farm auto share (personal, excluded)</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>1019.33</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>524 INSURANCE home share (Unit 2 50%, yellow proxy)</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>552.76</v>
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Geico auto credit (personal, excluded)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>-540.89</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>524 INSURANCE home share (Unit 1 50%, yellow proxy)</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="n">
-        <v>552.7</v>
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Inventory parked (Frame Up + LAMA + Hindman)</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>8043.22</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>State Farm auto share (personal, excluded)</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>1019.33</v>
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Extra Space HOLD</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Geico auto credit (personal, excluded)</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>-540.89</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Inventory parked (Frame Up + LAMA + Hindman)</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="n">
-        <v>8043.22</v>
-      </c>
-    </row>
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Soldier Field parking HOLD</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>Extra Space HOLD</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="n">
-        <v>360</v>
-      </c>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Checking inflows after answers 2026-09-18</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>Soldier Field parking HOLD</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60"/>
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>216 Oak Park STR / RENTAL INCOME (cash, Ava CONFIRMED co-tenant)</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Delach 8 × $1,450</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>11600</v>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Checking inflows 2026-09-18</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="n"/>
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ava Hernandez 8 × $500 (co-tenant CONFIRMED)</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>216 Oak Park STR / RENTAL INCOME (cash, incl. Ava yellow)</t>
-        </is>
-      </c>
-      <c r="B62" s="15" t="n">
-        <v>19500</v>
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Joan Friedberger 2 × $1,950 (Dec cash + Jan 2026 prepaid)</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>3900</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Delach 8 × $1,450</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="n">
-        <v>11600</v>
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Joan half-Nov $975 NOT booked (WAIT 8507)</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>975</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ava Hernandez 8 × $500 (ASK roommate)</t>
-        </is>
-      </c>
-      <c r="B64" s="15" t="n">
-        <v>4000</v>
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>216 INTERIOR MAINTENANCE Dec (Joan Zelle OUT repair)</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>675</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Joan Friedberger 2 × $1,950 (ASK Dec vs Jan prepaid)</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="n">
-        <v>3900</v>
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>EPGC Consultant (GCM removed)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>EPGC Consultant = GCM BOM = 1099-NEC</t>
+          <t>GCM personal 1099-NEC (tab + Income E7)</t>
         </is>
       </c>
       <c r="B66" s="9" t="n">
@@ -1166,7 +1160,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>GCM reimbursements EXCLUDED (9922 + 8507)</t>
+          <t>GCM reimbursements EXCLUDED (9922 + 8507; May 22 CONFIRMED)</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
@@ -1176,7 +1170,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Bear Creek gift EXCLUDED (4 × $9,500)</t>
+          <t>Bear Creek gift to Jake from parents EXCLUDED</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
@@ -1186,7 +1180,7 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>UTMA Thomas wires EXCLUDED (2 × $5,000)</t>
+          <t>UTMA Thomas wires EXCLUDED (2 × $5,000, not ~$10k each)</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
@@ -1196,7 +1190,7 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Freeman’s CIBC $11,000 12/24 HOLD</t>
+          <t>Art Sales Sale 6428 Sale Price (Cost TBD)</t>
         </is>
       </c>
       <c r="B70" s="15" t="n">

--- a/.cursor/scratch/tax_turbo_parts/ASK.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CONFIRMED 2026-09-18</t>
+          <t>CONFIRMED 2026-09-18 + 2026-09-20 locks</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -658,542 +658,564 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED. Previously home=Travelers, car=Geico. Only the HOME share of Prime State Farm is on 524 INSURANCE (50/50 U1/U2, yellow). Auto share and Geico $540.89 credit are personal. Split uses Feb 11 unbundled $157.53 home / $145.25 auto as the ratio.</t>
+          <t>CONFIRMED 2026-09-18. Only the HOME share of Prime State Farm is on 524 INSURANCE (50/50 U1/U2, yellow proxy). Auto share is personal — not EPGC, not 524. Split uses Feb 11 unbundled $157.53 home / $145.25 auto as the ratio.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Ava L Hernandez $500/mo rent</t>
+          <t>Travelers prior 524 home / Geico personal auto</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED Delach co-tenant. Keep eight $500 Zelle credits on 216 Oak Park STR / RENTAL INCOME. Delach $1,450 + Ava $500 = $1,950 unit rent (same as Joan later).</t>
+          <t>LOCKED 2026-09-20. User: “Traveler's was home insurance before for Ferdinand and Geico was for the cars.” Travelers = prior 524 Ferdinand homeowners (Units 1 and 2 keep the existing 50/50 home-share mapping — do not invent a new split). Any leftover Travelers 2025 (Jan leftover previously noted) is 524 INSURANCE / Sch E, not auto. $0 Travelers cash on Prime/Sapphire/BoA/Monarch. Geico = cars / personal auto. Geico $540.89 *AUTO credit already EXCLUDED personal. Do not put Geico on 524 INSURANCE or EPGC. Grove Collaborative ≠ 827 N Grove the house.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Oak Park vacant Oct + half Nov</t>
+          <t>Ava L Hernandez $500/mo rent</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED vacant October and the first half of November (held for rent). Occupancy: Delach/Ava through September; Joan from mid-November. Cash-basis months stay as deposited (Sep cash is $0 because September rent hit 8/29). Jan 2025 occupancy cash hit 12/31/2024 — still out of TY2025.</t>
+          <t>CONFIRMED Delach co-tenant. Keep eight $500 Zelle credits on 216 Oak Park STR / RENTAL INCOME. Delach $1,450 + Ava $500 = $1,950 unit rent (same as Joan later).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Joan 12/1 Zelle OUT $675 = repair</t>
+          <t>Oak Park vacant Oct + half Nov</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED. Checking 8507 Zelle to Joan 12/1 $675 → 216 INTERIOR MAINTENANCE (December). CPA may reclass interior vs exterior. 12/1 $1,950 IN on joint 0203 stays December occupancy cash; 12/31 $1,950 “January rent” stays Jan 2026 prepaid cash in TY2025.</t>
+          <t>CONFIRMED vacant October and the first half of November (held for rent). Occupancy: Delach/Ava through September; Joan from mid-November. Cash-basis months stay as deposited (Sep cash is $0 because September rent hit 8/29). Jan 2025 occupancy cash hit 12/31/2024 — still out of TY2025.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>GCM off EPGC Consultant</t>
+          <t>Joan 12/1 Zelle OUT $675 = repair</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED. BOM PAYMEN $21,500 stays on the GCM tab + Income E7 (personal 1099-NEC, Jacob’s name). EPGC Consultant zeroed. JAKE C / SEFOF reimbursements $5,214.69 still excluded.</t>
+          <t>CONFIRMED. Checking 8507 Zelle to Joan 12/1 $675 → 216 INTERIOR MAINTENANCE (December). CPA may reclass interior vs exterior. 12/1 $1,950 IN on joint 0203 stays December occupancy cash; 12/31 $1,950 “January rent” stays Jan 2026 prepaid cash in TY2025.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>May 22 Gates $609.02</t>
+          <t>GCM off EPGC Consultant</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED reimbursement (JAKE C, not BOM PAYMEN). Excluded from income.</t>
+          <t>CONFIRMED. BOM PAYMEN $21,500 stays on the GCM tab + Income E7 (personal 1099-NEC, Jacob’s name). EPGC Consultant zeroed. JAKE C / SEFOF reimbursements $5,214.69 still excluded.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Bear Creek $38,000 to Jake from parents</t>
+          <t>May 22 Gates $609.02</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED annual gift to Jacob from parents — not income. User: UTMA was not ~$10k each; Thomas wires $5,000 each (Emma CMA 2T48 + Phoebe CMA 4729) = $10,000 excluded.</t>
+          <t>CONFIRMED reimbursement (JAKE C, not BOM PAYMEN). Excluded from income.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Freeman’s / CIBC $11,000 art-sale settlement</t>
+          <t>Bear Creek $38,000 to Jake from parents</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CONFIRMED Sale 6428 Contract 303468. Check went to Megan (joint 0203 2025-12-24). Booked Art Sales Sale Price $11,000; Cost and object name yellow TBD. Not Mercury, not W-2 payroll.</t>
+          <t>CONFIRMED annual gift to Jacob from parents — not income. User: UTMA was not ~$10k each; Thomas wires $5,000 each (Emma CMA 2T48 + Phoebe CMA 4729) = $10,000 excluded.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Freeman’s / CIBC $11,000 art-sale settlement</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED Sale 6428 Contract 303468. Check went to Megan (joint 0203 2025-12-24). Booked Art Sales Sale Price $11,000; Cost and object name yellow TBD. Not Mercury, not W-2 payroll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>Checking 8507 statements</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>WAIT-MEGAN. Jacob asked Megan to send 2025 NOW 8507 statements.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>STILL OPEN</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>What to confirm</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>REMIND JACOB — ComEd with Megan</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Joint 0203 statements show ComEd ACH (e.g. 1/21 Jacob $59.04 + Megan $132.94). ComEd is not on these cards. Monarch Adv Plus shows ACH: Jacob Coley $829.15 → Unit 2 ELECTRIC; Megan Gerrard $1,565.26 → Unit 1 ELECTRIC (yellow). User: must have been paid directly or with a check. Double-check with Megan: meters, whether Jake checking ACH is the full picture, and any extra check/direct payments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Soldier Field East Parking $57</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Extra Space $360</t>
+          <t>Soldier Field East Parking $57</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
+          <t>Coinbase 2025-11-01 same day as Field Museum. Not confirmed — HOLD.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>State Farm declarations / Sep–Dec</t>
+          <t>Extra Space $360</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Home vs auto $ is a Feb-charge proxy ($157.53 home / $145.25 auto) until declarations pages. None on Prime Sep–Dec 2025 (524 sold 12/18 — those months may be another account). 2023–24 Excel booked all homeowners on U1; this packet 50/50’s the home share. No 2025 Travelers found on Prime/Sapphire/BoA/Monarch.</t>
+          <t>Prime 2025-12-10. Not part of the HD/Lowe’s/IKEA split — HOLD (storage vs moving vs personal).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Inventory object IDs</t>
+          <t>State Farm declarations / Sep–Dec</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
+          <t>Home vs auto $ of bundled State Farm is a Feb-charge proxy ($157.53 home / $145.25 auto) until declarations pages. None on Prime Sep–Dec 2025 (524 sold 12/18 — those months may be another account). 2023–24 Excel booked all homeowners on U1; this packet 50/50’s the home share (locked mapping — do not invent a new split). Travelers vs Geico identity is LOCKED 2026-09-20 — ASK no longer asks which carrier was home vs cars.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>827 N Grove the house — HD 1/3 vs locked CapEx</t>
+          <t>Inventory object IDs</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>HD/Lowe’s/IKEA 1/3 $604.12 is pre-close materials for 827 N Grove the house (Q5 split), not Grove Collaborative. Do NOT fold into locked TY2025 CapEx $53,660 until CPA says so.</t>
+          <t>Frame Up $536.41 + LAMA $6,821.06 + Hindman $282.24 + $403.51 parked off Cost total until objects named (avoid Mercury double count).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>WAIT MEGAN — Checking 8507 (NOW) 2025 statements</t>
+          <t>827 N Grove the house — HD 1/3 vs locked CapEx</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Jacob asked Megan to send them. Needed to (a) book Joan’s half-November rent if the deposit is there, (b) keep reconciling Airbnb/VRBO vs platform, (c) keep the three SEFOF reimbursements tied. 11/30 Zelle FROM MEGAN $1,950 on 8507 is a Megan transfer, not Joan rent.</t>
+          <t>HD/Lowe’s/IKEA 1/3 $604.12 is pre-close materials for 827 N Grove the house (Q5 split), not Grove Collaborative. Do NOT fold into locked TY2025 CapEx $53,660 until CPA says so.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Joan half-November rent $975</t>
+          <t>WAIT MEGAN — Checking 8507 (NOW) 2025 statements</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>User: Joan paid half of November. Not on joint 0203. Nov cash on 216 Oak Park stays $0 until 8507 (or another account) shows the deposit. Do not invent $975.</t>
+          <t>Jacob asked Megan to send them. Needed to (a) book Joan’s half-November rent if the deposit is there, (b) keep reconciling Airbnb/VRBO vs platform, (c) keep the three SEFOF reimbursements tied. 11/30 Zelle FROM MEGAN $1,950 on 8507 is a Megan transfer, not Joan rent.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t>Joan half-November rent $975</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>User: Joan paid half of November. Not on joint 0203. Nov cash on 216 Oak Park stays $0 until 8507 (or another account) shows the deposit. Do not invent $975.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>Sale 6428 object / Cost</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Freeman’s $11,000 is Art Sales Sale Price (check to Megan 12/24). Cost and object blank yellow — Income E8 net stays $0 until Cost is filled. 2026-01-08 Hindman SETTLEMENT SALE 6428 $937.83 is 2026, not TY2025.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Applied / split totals</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n">
-        <v>153</v>
-      </c>
+      <c r="B39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>March HD 100% 524 repairs</t>
+          <t>EPGC Travel (Park Chicago $100 + Field Museum $53)</t>
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>1358.65</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
+          <t>March HD 100% 524 repairs</t>
         </is>
       </c>
       <c r="B41" s="9" t="n">
-        <v>1812.46</v>
+        <v>1358.65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
+          <t>Remaining HD/Lowe’s/IKEA (split pool)</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>604.1799999999999</v>
+        <v>1812.46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+          <t>524 repairs from remaining 1/3 (then 50/50 U1/U2)</t>
         </is>
       </c>
       <c r="B43" s="9" t="n">
-        <v>981.4400000000001</v>
+        <v>604.1799999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
+          <t>Unit 2 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>981.4400000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
           <t>Unit 1 EXTERIOR add (March 50% + remaining 524-share 50%)</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B45" s="9" t="n">
         <v>981.39</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Personal 1/3 (excluded from P&amp;L)</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B46" s="11" t="n">
         <v>604.16</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>827 N Grove the house 1/3 HD/Lowe’s/IKEA (not Grove Collaborative; not locked $53,660)</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="n">
-        <v>604.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
+          <t>827 N Grove the house 1/3 HD/Lowe’s/IKEA (not Grove Collaborative; not locked $53,660)</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>604.12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
           <t>524 Unit 2 SUPPLIES (Grove Collaborative)</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n">
+      <c r="B48" s="9" t="n">
         <v>791.21</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n">
-        <v>829.15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
+          <t>Unit 2 ELECTRIC ComEd Jacob (YELLOW — ask Megan)</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>829.15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
           <t>Unit 1 ELECTRIC ComEd Megan (YELLOW — ask Megan)</t>
         </is>
       </c>
-      <c r="B49" s="13" t="n">
+      <c r="B50" s="13" t="n">
         <v>1565.26</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>524 INSURANCE home share (Unit 2 50%, yellow proxy)</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="n">
-        <v>552.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
+          <t>524 INSURANCE home share (Unit 2 50%, yellow proxy)</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n">
+        <v>552.76</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
           <t>524 INSURANCE home share (Unit 1 50%, yellow proxy)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="n">
+      <c r="B52" s="15" t="n">
         <v>552.7</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Travelers leftover Jan 2025 (524 home; $0 on cards/Monarch)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>State Farm auto share (personal, excluded)</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n">
+      <c r="B54" s="11" t="n">
         <v>1019.33</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Geico auto credit (personal, excluded)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n">
+      <c r="B55" s="11" t="n">
         <v>-540.89</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>Inventory parked (Frame Up + LAMA + Hindman)</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B56" s="9" t="n">
         <v>8043.22</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Extra Space HOLD</t>
         </is>
       </c>
-      <c r="B55" s="15" t="n">
+      <c r="B57" s="15" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>Soldier Field parking HOLD</t>
         </is>
       </c>
-      <c r="B56" s="15" t="n">
+      <c r="B58" s="15" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Checking inflows after answers 2026-09-18</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>216 Oak Park STR / RENTAL INCOME (cash, Ava CONFIRMED co-tenant)</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="n">
-        <v>19500</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Delach 8 × $1,450</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="n">
-        <v>11600</v>
-      </c>
+      <c r="B60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ava Hernandez 8 × $500 (co-tenant CONFIRMED)</t>
+          <t>216 Oak Park STR / RENTAL INCOME (cash, Ava CONFIRMED co-tenant)</t>
         </is>
       </c>
       <c r="B61" s="9" t="n">
-        <v>4000</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Joan Friedberger 2 × $1,950 (Dec cash + Jan 2026 prepaid)</t>
+          <t xml:space="preserve">  Delach 8 × $1,450</t>
         </is>
       </c>
       <c r="B62" s="9" t="n">
-        <v>3900</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Joan half-Nov $975 NOT booked (WAIT 8507)</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="n">
-        <v>975</v>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ava Hernandez 8 × $500 (co-tenant CONFIRMED)</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>216 INTERIOR MAINTENANCE Dec (Joan Zelle OUT repair)</t>
+          <t xml:space="preserve">  Joan Friedberger 2 × $1,950 (Dec cash + Jan 2026 prepaid)</t>
         </is>
       </c>
       <c r="B64" s="9" t="n">
-        <v>675</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>EPGC Consultant (GCM removed)</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>0</v>
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Joan half-Nov $975 NOT booked (WAIT 8507)</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>975</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>GCM personal 1099-NEC (tab + Income E7)</t>
+          <t>216 INTERIOR MAINTENANCE Dec (Joan Zelle OUT repair)</t>
         </is>
       </c>
       <c r="B66" s="9" t="n">
-        <v>21500</v>
+        <v>675</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>GCM reimbursements EXCLUDED (9922 + 8507; May 22 CONFIRMED)</t>
+          <t>EPGC Consultant (GCM removed)</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
-        <v>5214.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>Bear Creek gift to Jake from parents EXCLUDED</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="n">
-        <v>38000</v>
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>GCM personal 1099-NEC (tab + Income E7)</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>21500</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
+          <t>GCM reimbursements EXCLUDED (9922 + 8507; May 22 CONFIRMED)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>5214.69</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>Bear Creek gift to Jake from parents EXCLUDED</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
           <t>UTMA Thomas wires EXCLUDED (2 × $5,000, not ~$10k each)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="n">
+      <c r="B71" s="11" t="n">
         <v>10000</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>Art Sales Sale 6428 Sale Price (Cost TBD)</t>
         </is>
       </c>
-      <c r="B70" s="15" t="n">
+      <c r="B72" s="15" t="n">
         <v>11000</v>
       </c>
     </row>
